--- a/config/Coding/VF5NP_BPM_F108.xlsx
+++ b/config/Coding/VF5NP_BPM_F108.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\Coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E93C009-8D09-4EFC-BABC-EC573D03CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF1F224-CA72-490A-8DA5-6C587BDFAD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CFF97229-C12C-41CE-8DC6-FA55CCD0AA71}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" xr2:uid="{CFF97229-C12C-41CE-8DC6-FA55CCD0AA71}"/>
   </bookViews>
   <sheets>
     <sheet name="CDS Coding" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,6 @@
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
-    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="\">#N/A</definedName>
@@ -1401,7 +1400,7 @@
     <definedName name="AA\\\\\\">#REF!</definedName>
     <definedName name="AAA" localSheetId="0">#REF!</definedName>
     <definedName name="AAA">#REF!</definedName>
-    <definedName name="aaaa">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaaa">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="aaaaa" hidden="1">{"RES-2000",#N/A,FALSE,"BL2000";"A1-2000",#N/A,FALSE,"BL2000";"A2-2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaa" hidden="1">{"RES-2002",#N/A,FALSE,"BL2000";"A1-2002",#N/A,FALSE,"BL2000";"A2-2002",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="aaaaaaa" hidden="1">{"B10-2000",#N/A,FALSE,"BL2000"}</definedName>
@@ -1413,8 +1412,8 @@
     <definedName name="AAAAAAAAAAAAAAAA">RunParT</definedName>
     <definedName name="aaaaaaaaaaaaaaaaa" hidden="1">{"AnaM1",#N/A,FALSE,"AnalisisM";"AnaM2",#N/A,FALSE,"AnalisisM";"AnaM3",#N/A,FALSE,"AnalisisM"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaaaaaaaaaa" hidden="1">{"COMJPN2000",#N/A,FALSE,"BL2000"}</definedName>
-    <definedName name="aaab">[2]Selections!$A$2:$A$103</definedName>
-    <definedName name="aac">[2]Selections!$A$2:$A$103</definedName>
+    <definedName name="aaab">[1]Selections!$A$2:$A$103</definedName>
+    <definedName name="aac">[1]Selections!$A$2:$A$103</definedName>
     <definedName name="ab" hidden="1">{"HS_USA",#N/A,FALSE,"Base"}</definedName>
     <definedName name="ABC" hidden="1">{"INCPRE2000",#N/A,FALSE,"BL2000"}</definedName>
     <definedName name="abcd" hidden="1">{"PT2000",#N/A,FALSE,"BL2000"}</definedName>
@@ -1426,7 +1425,7 @@
     <definedName name="abs">#REF!</definedName>
     <definedName name="Acc" localSheetId="0">#REF!</definedName>
     <definedName name="Acc">#REF!</definedName>
-    <definedName name="Access_Attribute">[2]Selections!$H$2:$H$4</definedName>
+    <definedName name="Access_Attribute">[1]Selections!$H$2:$H$4</definedName>
     <definedName name="Access_Button" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button1" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
     <definedName name="Access_Button2" hidden="1">"機能ｺｰﾄﾞ一覧_BLK→機能_List"</definedName>
@@ -1455,7 +1454,7 @@
     <definedName name="AK">#REF!</definedName>
     <definedName name="ALE" localSheetId="0">#REF!</definedName>
     <definedName name="ALE">#REF!</definedName>
-    <definedName name="Alert_Behaviour">[2]Selections!$G$2:$G$7</definedName>
+    <definedName name="Alert_Behaviour">[1]Selections!$G$2:$G$7</definedName>
     <definedName name="ALG_24" localSheetId="0">#REF!</definedName>
     <definedName name="ALG_24">#REF!</definedName>
     <definedName name="ALG_24_low" localSheetId="0">#REF!</definedName>
@@ -1534,8 +1533,8 @@
     <definedName name="apr_retail">#REF!</definedName>
     <definedName name="april" localSheetId="0">#REF!</definedName>
     <definedName name="april">#REF!</definedName>
-    <definedName name="Area" localSheetId="0">[3]Selections!$I$1:$I$2</definedName>
-    <definedName name="Area">[4]Selections!$I$1:$I$2</definedName>
+    <definedName name="Area" localSheetId="0">[2]Selections!$I$1:$I$2</definedName>
+    <definedName name="Area">[3]Selections!$I$1:$I$2</definedName>
     <definedName name="AREA_COVER" localSheetId="0">#REF!</definedName>
     <definedName name="AREA_COVER">#REF!</definedName>
     <definedName name="Arial" localSheetId="0">#REF!</definedName>
@@ -1558,8 +1557,8 @@
     <definedName name="Attachment">#REF!</definedName>
     <definedName name="Attachment_4_all" localSheetId="0">#REF!</definedName>
     <definedName name="Attachment_4_all">#REF!</definedName>
-    <definedName name="Audience" localSheetId="0">[3]Selections!$C$1:$C$7</definedName>
-    <definedName name="Audience">[4]Selections!$C$1:$C$7</definedName>
+    <definedName name="Audience" localSheetId="0">[2]Selections!$C$1:$C$7</definedName>
+    <definedName name="Audience">[3]Selections!$C$1:$C$7</definedName>
     <definedName name="august" localSheetId="0">#REF!</definedName>
     <definedName name="august">#REF!</definedName>
     <definedName name="B" localSheetId="0">#REF!</definedName>
@@ -1657,7 +1656,7 @@
     <definedName name="check" localSheetId="0">#REF!</definedName>
     <definedName name="check">#REF!</definedName>
     <definedName name="CHECK_1">"チェック 65"</definedName>
-    <definedName name="Check_Per_Cycle">[2]Selections!$J$2:$J$4</definedName>
+    <definedName name="Check_Per_Cycle">[1]Selections!$J$2:$J$4</definedName>
     <definedName name="Chicago" localSheetId="0">#REF!</definedName>
     <definedName name="Chicago">#REF!</definedName>
     <definedName name="cmprtl_dir" localSheetId="0">#REF!</definedName>
@@ -1824,8 +1823,8 @@
     <definedName name="Dealer_Gross_Retail">#REF!</definedName>
     <definedName name="december" localSheetId="0">#REF!</definedName>
     <definedName name="december">#REF!</definedName>
-    <definedName name="Decode_Type" localSheetId="0">[3]Selections!$F$1:$F$9</definedName>
-    <definedName name="Decode_Type">[4]Selections!$F$1:$F$9</definedName>
+    <definedName name="Decode_Type" localSheetId="0">[2]Selections!$F$1:$F$9</definedName>
+    <definedName name="Decode_Type">[3]Selections!$F$1:$F$9</definedName>
     <definedName name="Desc" localSheetId="0">#REF!</definedName>
     <definedName name="Desc">#REF!</definedName>
     <definedName name="DEST" localSheetId="0">#REF!</definedName>
@@ -1848,8 +1847,8 @@
     <definedName name="Di">#REF!</definedName>
     <definedName name="DIC" localSheetId="0">#REF!</definedName>
     <definedName name="DIC">#REF!</definedName>
-    <definedName name="DID_Group" localSheetId="0">[3]Selections!$E$1:$E$6</definedName>
-    <definedName name="DID_Group">[4]Selections!$E$1:$E$6</definedName>
+    <definedName name="DID_Group" localSheetId="0">[2]Selections!$E$1:$E$6</definedName>
+    <definedName name="DID_Group">[3]Selections!$E$1:$E$6</definedName>
     <definedName name="digit_18">"テキスト 21"</definedName>
     <definedName name="Dimax" localSheetId="0">#REF!</definedName>
     <definedName name="Dimax">#REF!</definedName>
@@ -1896,7 +1895,7 @@
     <definedName name="DSFGSDFG" localSheetId="0">#REF!</definedName>
     <definedName name="DSFGSDFG">#REF!</definedName>
     <definedName name="dsfsf" hidden="1">{"SUM GER",#N/A,FALSE,"SUM GER";"SUM FRA",#N/A,FALSE,"SUM FRA";"SUM ITA",#N/A,FALSE,"SUM ITA";"SUM SPA",#N/A,FALSE,"SUM SPA";"SUM EGB",#N/A,FALSE,"SUM EGB";"SUM IND",#N/A,FALSE,"SUM IND"}</definedName>
-    <definedName name="DTC_Class">[2]Selections!$F$2:$F$7</definedName>
+    <definedName name="DTC_Class">[1]Selections!$F$2:$F$7</definedName>
     <definedName name="DTEXT" localSheetId="0">#REF!</definedName>
     <definedName name="DTEXT">#REF!</definedName>
     <definedName name="DUMMY" localSheetId="0">#REF!</definedName>
@@ -1925,7 +1924,7 @@
     <definedName name="Eb">#REF!</definedName>
     <definedName name="EcartFranchise" localSheetId="0">#REF!</definedName>
     <definedName name="EcartFranchise">#REF!</definedName>
-    <definedName name="ECUDID1">[5]Selections!$I$1:$I$2</definedName>
+    <definedName name="ECUDID1">[4]Selections!$I$1:$I$2</definedName>
     <definedName name="EE" localSheetId="0">#REF!</definedName>
     <definedName name="EE">#REF!</definedName>
     <definedName name="EE\" localSheetId="0">#REF!</definedName>
@@ -2077,7 +2076,7 @@
     <definedName name="FactoryResultUpdate" localSheetId="0">#REF!</definedName>
     <definedName name="FactoryResultUpdate">#REF!</definedName>
     <definedName name="fasdf" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
-    <definedName name="FaultList1">[6]Selections!$H$2:$H$4</definedName>
+    <definedName name="FaultList1">[5]Selections!$H$2:$H$4</definedName>
     <definedName name="ｆｃ" localSheetId="0">#REF!</definedName>
     <definedName name="ｆｃ">#REF!</definedName>
     <definedName name="FC_MES_MIX_CON_PROD_PARA_VANESSA" localSheetId="0">#REF!</definedName>
@@ -2331,8 +2330,8 @@
     <definedName name="hdfghfg" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="HEV" localSheetId="0">#REF!</definedName>
     <definedName name="HEV">#REF!</definedName>
-    <definedName name="Hex_LB" localSheetId="0">[7]Selections!$A$2:$A$103</definedName>
-    <definedName name="Hex_LB">[8]Selections!$A$2:$A$103</definedName>
+    <definedName name="Hex_LB" localSheetId="0">[6]Selections!$A$2:$A$103</definedName>
+    <definedName name="Hex_LB">[7]Selections!$A$2:$A$103</definedName>
     <definedName name="HF1_HARN">#N/A</definedName>
     <definedName name="ｈｇｈｆｇ" localSheetId="0">InpMove5</definedName>
     <definedName name="ｈｇｈｆｇ">InpMove5</definedName>
@@ -2371,8 +2370,8 @@
     <definedName name="IF">#REF!</definedName>
     <definedName name="II" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="II" hidden="1">#REF!</definedName>
-    <definedName name="Implementation" localSheetId="0">[3]Selections!$I$1:$I$2</definedName>
-    <definedName name="Implementation">[4]Selections!$I$1:$I$2</definedName>
+    <definedName name="Implementation" localSheetId="0">[2]Selections!$I$1:$I$2</definedName>
+    <definedName name="Implementation">[3]Selections!$I$1:$I$2</definedName>
     <definedName name="INC" localSheetId="0">#REF!</definedName>
     <definedName name="INC">#REF!</definedName>
     <definedName name="INDENT">#N/A</definedName>
@@ -2706,8 +2705,8 @@
     <definedName name="MDL">#REF!</definedName>
     <definedName name="MDLYR" localSheetId="0">#REF!</definedName>
     <definedName name="MDLYR">#REF!</definedName>
-    <definedName name="Memory" localSheetId="0">[3]Selections!$G$1:$G$4</definedName>
-    <definedName name="Memory">[4]Selections!$G$1:$G$4</definedName>
+    <definedName name="Memory" localSheetId="0">[2]Selections!$G$1:$G$4</definedName>
+    <definedName name="Memory">[3]Selections!$G$1:$G$4</definedName>
     <definedName name="Memphis_a" localSheetId="0">#REF!</definedName>
     <definedName name="Memphis_a">#REF!</definedName>
     <definedName name="MENU" localSheetId="0">#REF!</definedName>
@@ -2780,9 +2779,9 @@
     <definedName name="month3_lease">#REF!</definedName>
     <definedName name="MOTO" localSheetId="0">#REF!</definedName>
     <definedName name="MOTO">#REF!</definedName>
-    <definedName name="MSB_LSB" localSheetId="0">[3]Selections!$B$1:$B$3</definedName>
-    <definedName name="MSB_LSB">[4]Selections!$B$1:$B$3</definedName>
-    <definedName name="MSB_LSB_List">[9]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB" localSheetId="0">[2]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB">[3]Selections!$B$1:$B$3</definedName>
+    <definedName name="MSB_LSB_List">[8]Selections!$B$1:$B$3</definedName>
     <definedName name="MSRP" localSheetId="0">#REF!</definedName>
     <definedName name="MSRP">#REF!</definedName>
     <definedName name="MSRP95" localSheetId="0">#REF!</definedName>
@@ -2877,8 +2876,8 @@
     <definedName name="NNN">#REF!</definedName>
     <definedName name="no" localSheetId="0">#REF!</definedName>
     <definedName name="no">#REF!</definedName>
-    <definedName name="No_Yes" localSheetId="0">[3]Selections!$A$1:$A$3</definedName>
-    <definedName name="No_Yes">[4]Selections!$A$1:$A$3</definedName>
+    <definedName name="No_Yes" localSheetId="0">[2]Selections!$A$1:$A$3</definedName>
+    <definedName name="No_Yes">[3]Selections!$A$1:$A$3</definedName>
     <definedName name="Noff" localSheetId="0">#REF!</definedName>
     <definedName name="Noff">#REF!</definedName>
     <definedName name="Ｎｏｓ" localSheetId="0">#REF!</definedName>
@@ -2965,20 +2964,20 @@
     <definedName name="P_3">#REF!</definedName>
     <definedName name="P_IMｸﾞﾗﾌ" localSheetId="0">#REF!</definedName>
     <definedName name="P_IMｸﾞﾗﾌ">#REF!</definedName>
-    <definedName name="P2_DIDs" localSheetId="0">[10]Ref_Ranges!$AI$2:$AI$3</definedName>
-    <definedName name="P2_DIDs">[11]Ref_Ranges!$AI$2:$AI$3</definedName>
-    <definedName name="P2_ECUPins" localSheetId="0">OFFSET([12]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[12]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[12]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
-    <definedName name="P2_ECUPins">OFFSET([13]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[13]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[13]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
-    <definedName name="P2_ECUType" localSheetId="0">[10]Header!$D$139:$D$150</definedName>
-    <definedName name="P2_ECUType">[11]Header!$D$139:$D$150</definedName>
-    <definedName name="P2_ExtDataList" localSheetId="0">[10]Ref_Ranges!$AE$2:$AE$4</definedName>
-    <definedName name="P2_ExtDataList">[11]Ref_Ranges!$AE$2:$AE$4</definedName>
-    <definedName name="P2_LSDIDList" localSheetId="0">[10]Ref_Ranges!$X$2:$X$4</definedName>
-    <definedName name="P2_LSDIDList">[11]Ref_Ranges!$X$2:$X$4</definedName>
-    <definedName name="P2_SSD3SymtomValidator" localSheetId="0">[10]Ref_Ranges!$AK$2:$AK$3</definedName>
-    <definedName name="P2_SSD3SymtomValidator">[11]Ref_Ranges!$AK$2:$AK$3</definedName>
-    <definedName name="P2_Symptom_Validator" localSheetId="0">OFFSET([10]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[10]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[10]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
-    <definedName name="P2_Symptom_Validator">OFFSET([11]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[11]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[11]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
+    <definedName name="P2_DIDs" localSheetId="0">[9]Ref_Ranges!$AI$2:$AI$3</definedName>
+    <definedName name="P2_DIDs">[10]Ref_Ranges!$AI$2:$AI$3</definedName>
+    <definedName name="P2_ECUPins" localSheetId="0">OFFSET([11]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[11]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[11]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
+    <definedName name="P2_ECUPins">OFFSET([12]Ref_Ranges!$N$1,1,0,IF(MATCH("*",[12]Ref_Ranges!$N:$N,-1)&gt;2,MATCH("*",[12]Ref_Ranges!$N:$N,-1),3)-1,1)</definedName>
+    <definedName name="P2_ECUType" localSheetId="0">[9]Header!$D$139:$D$150</definedName>
+    <definedName name="P2_ECUType">[10]Header!$D$139:$D$150</definedName>
+    <definedName name="P2_ExtDataList" localSheetId="0">[9]Ref_Ranges!$AE$2:$AE$4</definedName>
+    <definedName name="P2_ExtDataList">[10]Ref_Ranges!$AE$2:$AE$4</definedName>
+    <definedName name="P2_LSDIDList" localSheetId="0">[9]Ref_Ranges!$X$2:$X$4</definedName>
+    <definedName name="P2_LSDIDList">[10]Ref_Ranges!$X$2:$X$4</definedName>
+    <definedName name="P2_SSD3SymtomValidator" localSheetId="0">[9]Ref_Ranges!$AK$2:$AK$3</definedName>
+    <definedName name="P2_SSD3SymtomValidator">[10]Ref_Ranges!$AK$2:$AK$3</definedName>
+    <definedName name="P2_Symptom_Validator" localSheetId="0">OFFSET([9]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[9]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[9]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
+    <definedName name="P2_Symptom_Validator">OFFSET([10]Ref_Ranges!$P$1,1,0,IF(MATCH("*",[10]Ref_Ranges!$P:$P,-1)&gt;2,MATCH("*",[10]Ref_Ranges!$P:$P,-1),3)-1,1)</definedName>
     <definedName name="P6改" hidden="1">{"SUM ALL YR",#N/A,FALSE,"SUM ALL YR";"sum01",#N/A,FALSE,"SUM 01";"sumM2",#N/A,FALSE,"SUM M2";"sum02",#N/A,FALSE,"SUM 02";"sum03",#N/A,FALSE,"SUM 03";"sum04",#N/A,FALSE,"SUM 04";"sum05",#N/A,FALSE,"SUM 05"}</definedName>
     <definedName name="PACOST" localSheetId="0">#REF!</definedName>
     <definedName name="PACOST">#REF!</definedName>
@@ -3016,7 +3015,7 @@
     <definedName name="Payment_24">#REF!</definedName>
     <definedName name="Payment_36" localSheetId="0">#REF!</definedName>
     <definedName name="Payment_36">#REF!</definedName>
-    <definedName name="PBCU_Codes">[2]Selections!$D$2:$D$5</definedName>
+    <definedName name="PBCU_Codes">[1]Selections!$D$2:$D$5</definedName>
     <definedName name="PCAT" localSheetId="0">#REF!</definedName>
     <definedName name="PCAT">#REF!</definedName>
     <definedName name="PDSPEC" localSheetId="0">#REF!</definedName>
@@ -3134,7 +3133,7 @@
     <definedName name="PRINTVA">#REF!</definedName>
     <definedName name="PRINTW" localSheetId="0">#REF!</definedName>
     <definedName name="PRINTW">#REF!</definedName>
-    <definedName name="Priority">[2]Selections!$I$2:$I$6</definedName>
+    <definedName name="Priority">[1]Selections!$I$2:$I$6</definedName>
     <definedName name="Prix" localSheetId="0">#REF!</definedName>
     <definedName name="Prix">#REF!</definedName>
     <definedName name="PRT" localSheetId="0">#REF!</definedName>
@@ -3196,8 +3195,8 @@
     <definedName name="Q従業員名簿ｴｸｽﾎﾟｰﾄ用">#REF!</definedName>
     <definedName name="R_FLUSH_B1..M10" localSheetId="0">#REF!</definedName>
     <definedName name="R_FLUSH_B1..M10">#REF!</definedName>
-    <definedName name="R_IO_W" localSheetId="0">[3]Selections!$D$1:$D$9</definedName>
-    <definedName name="R_IO_W">[4]Selections!$D$1:$D$9</definedName>
+    <definedName name="R_IO_W" localSheetId="0">[2]Selections!$D$1:$D$9</definedName>
+    <definedName name="R_IO_W">[3]Selections!$D$1:$D$9</definedName>
     <definedName name="RANGE" localSheetId="0">#REF!</definedName>
     <definedName name="RANGE">#REF!</definedName>
     <definedName name="RANGE1" localSheetId="0">#REF!</definedName>
@@ -3227,8 +3226,8 @@
     <definedName name="repurch_base">#REF!</definedName>
     <definedName name="repurch_enter" localSheetId="0">#REF!</definedName>
     <definedName name="repurch_enter">#REF!</definedName>
-    <definedName name="Req_5" localSheetId="0">'[14]1.General'!#REF!</definedName>
-    <definedName name="Req_5">'[14]1.General'!#REF!</definedName>
+    <definedName name="Req_5" localSheetId="0">'[13]1.General'!#REF!</definedName>
+    <definedName name="Req_5">'[13]1.General'!#REF!</definedName>
     <definedName name="RES__24" localSheetId="0">#REF!</definedName>
     <definedName name="RES__24">#REF!</definedName>
     <definedName name="RES__36" localSheetId="0">#REF!</definedName>
@@ -3318,7 +3317,7 @@
     <definedName name="ｒてれ">ｇｇｇｒ</definedName>
     <definedName name="ｒふぇえ" localSheetId="0">InpMove6</definedName>
     <definedName name="ｒふぇえ">InpMove6</definedName>
-    <definedName name="s">[15]Selections!$I$2:$I$6</definedName>
+    <definedName name="s">[14]Selections!$I$2:$I$6</definedName>
     <definedName name="S\" localSheetId="0">#REF!</definedName>
     <definedName name="S\">#REF!</definedName>
     <definedName name="S\\" localSheetId="0">#REF!</definedName>
@@ -3365,8 +3364,8 @@
     <definedName name="ｓｄふぁｓｆだｓｄふぁｓｆあせｆあｓｆだｓ">#REF!</definedName>
     <definedName name="se" localSheetId="0">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
     <definedName name="se">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
-    <definedName name="Security_Required" localSheetId="0">[3]Selections!$H$1:$H$3</definedName>
-    <definedName name="Security_Required">[4]Selections!$H$1:$H$3</definedName>
+    <definedName name="Security_Required" localSheetId="0">[2]Selections!$H$1:$H$3</definedName>
+    <definedName name="Security_Required">[3]Selections!$H$1:$H$3</definedName>
     <definedName name="Segment_Sales" localSheetId="0">#REF!</definedName>
     <definedName name="Segment_Sales">#REF!</definedName>
     <definedName name="segment_share" localSheetId="0">#REF!</definedName>
@@ -3482,7 +3481,7 @@
     <definedName name="TEST">#REF!</definedName>
     <definedName name="text" localSheetId="0">#REF!</definedName>
     <definedName name="text">#REF!</definedName>
-    <definedName name="Text_LB">[2]Selections!$B$2:$B$103</definedName>
+    <definedName name="Text_LB">[1]Selections!$B$2:$B$103</definedName>
     <definedName name="texy" localSheetId="0">#REF!</definedName>
     <definedName name="texy">#REF!</definedName>
     <definedName name="ｔｇで" localSheetId="0">TMdatadisp1</definedName>
@@ -3803,8 +3802,8 @@
     <definedName name="ｘ81ｂ01">#N/A</definedName>
     <definedName name="XX" localSheetId="0">XX</definedName>
     <definedName name="XX">#N/A</definedName>
-    <definedName name="xxa1">[16]DataBlock!#REF!</definedName>
-    <definedName name="xxx1">[16]DataBlock!#REF!</definedName>
+    <definedName name="xxa1">[15]DataBlock!#REF!</definedName>
+    <definedName name="xxx1">[15]DataBlock!#REF!</definedName>
     <definedName name="Y">#N/A</definedName>
     <definedName name="Y\" localSheetId="0">#REF!</definedName>
     <definedName name="Y\">#REF!</definedName>
@@ -3818,12 +3817,12 @@
     <definedName name="Y\\\\\">#REF!</definedName>
     <definedName name="Y\\\\\\" localSheetId="0">#REF!</definedName>
     <definedName name="Y\\\\\\">#REF!</definedName>
-    <definedName name="yaa1">[16]DataBlock!#REF!</definedName>
+    <definedName name="yaa1">[15]DataBlock!#REF!</definedName>
     <definedName name="yes" localSheetId="0">#REF!</definedName>
     <definedName name="yes">#REF!</definedName>
-    <definedName name="yes_no">[2]Selections!$E$2:$E$3</definedName>
+    <definedName name="yes_no">[1]Selections!$E$2:$E$3</definedName>
     <definedName name="ｙｙｒｔ">#N/A</definedName>
-    <definedName name="yyy1">[16]DataBlock!#REF!</definedName>
+    <definedName name="yyy1">[15]DataBlock!#REF!</definedName>
     <definedName name="z" hidden="1">{"RESUMEN",#N/A,FALSE,"BASE ANEXOS";"ANEXO 1",#N/A,FALSE,"BASE ANEXOS";"ANEXO 2",#N/A,FALSE,"BASE ANEXOS"}</definedName>
     <definedName name="Z\" localSheetId="0">#REF!</definedName>
     <definedName name="Z\">#REF!</definedName>
@@ -3869,7 +3868,7 @@
     <definedName name="Ｚｓ">#REF!</definedName>
     <definedName name="ZZ" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="ZZ" hidden="1">#REF!</definedName>
-    <definedName name="zzz1">[16]DataBlock!#REF!</definedName>
+    <definedName name="zzz1">[15]DataBlock!#REF!</definedName>
     <definedName name="α" localSheetId="0">#REF!</definedName>
     <definedName name="α">#REF!</definedName>
     <definedName name="αf" localSheetId="0">#REF!</definedName>
@@ -4221,7 +4220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>Format Byte</t>
   </si>
@@ -4236,9 +4235,6 @@
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>from 2000 to 2099</t>
   </si>
   <si>
     <t>Vehicle Name</t>
@@ -4294,15 +4290,6 @@
 0x1=VF3NP
 0x2=VF5NP
 0x3=VF6NP
-0xFF=Invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-0x0=Unsupported
-0x10 - 0x1F = STANDARD
-0x20 - 0x5F = Full Options
-0x60 - 0x8F = TECH
-0x90 - 0xFE = Reserved
 0xFF=Invalid</t>
   </si>
   <si>
@@ -4425,6 +4412,249 @@
 0x1=Without 
 0x2=With 
 0xF=Invalid</t>
+  </si>
+  <si>
+    <t>0x00 = Unsupported
+0x10 = STANDARD
+0x11 = STANDARD
+0x12 = STANDARD
+0x13 = STANDARD
+0x14 = STANDARD
+0x15 = STANDARD
+0x16 = STANDARD
+0x17 = STANDARD
+0x18 = STANDARD
+0x19 = STANDARD
+0x1A = STANDARD
+0x1B = STANDARD
+0x1C = STANDARD
+0x1D = STANDARD
+0x1E = STANDARD
+0x1F = STANDARD
+0x20 = Full Options
+0x21 = Full Options
+0x22 = Full Options
+0x23 = Full Options
+0x24 = Full Options
+0x25 = Full Options
+0x26 = Full Options
+0x27 = Full Options
+0x28 = Full Options
+0x29 = Full Options
+0x2A = Full Options
+0x2B = Full Options
+0x2C = Full Options
+0x2D = Full Options
+0x2E = Full Options
+0x2F = Full Options
+0x30 = Full Options
+0x31 = Full Options
+0x32 = Full Options
+0x33 = Full Options
+0x34 = Full Options
+0x35 = Full Options
+0x36 = Full Options
+0x37 = Full Options
+0x38 = Full Options
+0x39 = Full Options
+0x3A = Full Options
+0x3B = Full Options
+0x3C = Full Options
+0x3D = Full Options
+0x3E = Full Options
+0x3F = Full Options
+0x40 = Full Options
+0x41 = Full Options
+0x42 = Full Options
+0x43 = Full Options
+0x44 = Full Options
+0x45 = Full Options
+0x46 = Full Options
+0x47 = Full Options
+0x48 = Full Options
+0x49 = Full Options
+0x4A = Full Options
+0x4B = Full Options
+0x4C = Full Options
+0x4D = Full Options
+0x4E = Full Options
+0x4F = Full Options
+0x50 = Full Options
+0x51 = Full Options
+0x52 = Full Options
+0x53 = Full Options
+0x54 = Full Options
+0x55 = Full Options
+0x56 = Full Options
+0x57 = Full Options
+0x58 = Full Options
+0x59 = Full Options
+0x5A = Full Options
+0x5B = Full Options
+0x5C = Full Options
+0x5D = Full Options
+0x5E = Full Options
+0x5F = Full Options
+0x60 = TECH
+0x61 = TECH
+0x62 = TECH
+0x63 = TECH
+0x64 = TECH
+0x65 = TECH
+0x66 = TECH
+0x67 = TECH
+0x68 = TECH
+0x69 = TECH
+0x6A = TECH
+0x6B = TECH
+0x6C = TECH
+0x6D = TECH
+0x6E = TECH
+0x6F = TECH
+0x70 = TECH
+0x71 = TECH
+0x72 = TECH
+0x73 = TECH
+0x74 = TECH
+0x75 = TECH
+0x76 = TECH
+0x77 = TECH
+0x78 = TECH
+0x79 = TECH
+0x7A = TECH
+0x7B = TECH
+0x7C = TECH
+0x7D = TECH
+0x7E = TECH
+0x7F = TECH
+0x80 = TECH
+0x81 = TECH
+0x82 = TECH
+0x83 = TECH
+0x84 = TECH
+0x85 = TECH
+0x86 = TECH
+0x87 = TECH
+0x88 = TECH
+0x89 = TECH
+0x8A = TECH
+0x8B = TECH
+0x8C = TECH
+0x8D = TECH
+0x8E = TECH
+0x8F = TECH
+0x90 = Reserved
+0x91 = Reserved
+0x92 = Reserved
+0x93 = Reserved
+0x94 = Reserved
+0x95 = Reserved
+0x96 = Reserved
+0x97 = Reserved
+0x98 = Reserved
+0x99 = Reserved
+0x9A = Reserved
+0x9B = Reserved
+0x9C = Reserved
+0x9D = Reserved
+0x9E = Reserved
+0x9F = Reserved
+0xA0 = Reserved
+0xA1 = Reserved
+0xA2 = Reserved
+0xA3 = Reserved
+0xA4 = Reserved
+0xA5 = Reserved
+0xA6 = Reserved
+0xA7 = Reserved
+0xA8 = Reserved
+0xA9 = Reserved
+0xAA = Reserved
+0xAB = Reserved
+0xAC = Reserved
+0xAD = Reserved
+0xAE = Reserved
+0xAF = Reserved
+0xB0 = Reserved
+0xB1 = Reserved
+0xB2 = Reserved
+0xB3 = Reserved
+0xB4 = Reserved
+0xB5 = Reserved
+0xB6 = Reserved
+0xB7 = Reserved
+0xB8 = Reserved
+0xB9 = Reserved
+0xBA = Reserved
+0xBB = Reserved
+0xBC = Reserved
+0xBD = Reserved
+0xBE = Reserved
+0xBF = Reserved
+0xC0 = Reserved
+0xC1 = Reserved
+0xC2 = Reserved
+0xC3 = Reserved
+0xC4 = Reserved
+0xC5 = Reserved
+0xC6 = Reserved
+0xC7 = Reserved
+0xC8 = Reserved
+0xC9 = Reserved
+0xCA = Reserved
+0xCB = Reserved
+0xCC = Reserved
+0xCD = Reserved
+0xCE = Reserved
+0xCF = Reserved
+0xD0 = Reserved
+0xD1 = Reserved
+0xD2 = Reserved
+0xD3 = Reserved
+0xD4 = Reserved
+0xD5 = Reserved
+0xD6 = Reserved
+0xD7 = Reserved
+0xD8 = Reserved
+0xD9 = Reserved
+0xDA = Reserved
+0xDB = Reserved
+0xDC = Reserved
+0xDD = Reserved
+0xDE = Reserved
+0xDF = Reserved
+0xE0 = Reserved
+0xE1 = Reserved
+0xE2 = Reserved
+0xE3 = Reserved
+0xE4 = Reserved
+0xE5 = Reserved
+0xE6 = Reserved
+0xE7 = Reserved
+0xE8 = Reserved
+0xE9 = Reserved
+0xEA = Reserved
+0xEB = Reserved
+0xEC = Reserved
+0xED = Reserved
+0xEE = Reserved
+0xEF = Reserved
+0xF0 = Reserved
+0xF1 = Reserved
+0xF2 = Reserved
+0xF3 = Reserved
+0xF4 = Reserved
+0xF5 = Reserved
+0xF6 = Reserved
+0xF7 = Reserved
+0xF8 = Reserved
+0xF9 = Reserved
+0xFA = Reserved
+0xFB = Reserved
+0xFC = Reserved
+0xFD = Reserved
+0xFE = Reserved
+0xFF = Invalid</t>
   </si>
 </sst>
 </file>
@@ -5196,50 +5426,934 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Document Regulation"/>
-      <sheetName val="Change Log &amp; General Info"/>
-      <sheetName val="Diagnostics Services"/>
-      <sheetName val="System DID"/>
-      <sheetName val="ECU DID"/>
-      <sheetName val="DTC-List"/>
-      <sheetName val="FTB_RepairAction Refer"/>
-      <sheetName val="ECU Component data sheet"/>
-      <sheetName val="Snapshot DIDs"/>
-      <sheetName val="Extended Data"/>
-      <sheetName val="Routines Data (0x31)"/>
-      <sheetName val="Basic DIDs Check"/>
-      <sheetName val="Write VIN"/>
-      <sheetName val="ECU Exchange"/>
-      <sheetName val="Flashing Sequence"/>
-      <sheetName val="VOD Coding"/>
-      <sheetName val="CDS Coding"/>
-      <sheetName val="IO Control (2F)"/>
-      <sheetName val="Calibration Sequence"/>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Fault List"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="PDU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>no sub type information</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Body</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>No</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>A1</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>MO</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>Gen</v>
+          </cell>
+          <cell r="I2">
+            <v>1</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>OPC</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>01</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>General Electrical Failure</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Chassis</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Yes</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>A2</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>WLO</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>Dev</v>
+          </cell>
+          <cell r="I3">
+            <v>2</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>MPC</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>02</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>General signal failure</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>Network</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>B</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>WLB</v>
+          </cell>
+          <cell r="I4">
+            <v>3</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>See FDC Strategy Columns</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>03</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>FM (Frequency Modulated) / PWM (Pulse Width Modulated) Failure</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Powertrain</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>C</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Generic Warning Text</v>
+          </cell>
+          <cell r="I5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>04</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>System Internal Failures</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>D</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>Specific Warning Text</v>
+          </cell>
+          <cell r="I6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>05</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>System Programming Failures</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>E</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>None</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>06</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Algorithm Based Failures</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>07</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Mechanical Failures</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>08</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Bus Signal / Message Failures</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>09</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Component Failures</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>circuit short to ground</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>circuit short to battery</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>circuit open</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>circuit short to ground or open</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>circuit short to battery or open</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>circuit voltage below threshold</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>circuit voltage above threshold</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>circuit current below threshold</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>circuit current above threshold</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>1A</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>circuit resistance below threshold</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>1B</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>circuit resistance above threshold</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>1C</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>circuit voltage out of range</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>1D</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>circuit current out of range</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>1E</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>circuit resistance out of range</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>1F</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>circuit intermittent</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>21</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>signal amplitude &lt; minimum</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>22</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>signal amplitude &gt; maximum</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>23</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>signal stuck low</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>24</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>signal stuck high</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>25</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>signal shape / waveform failure</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>26</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>signal rate of change below threshold</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>27</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>signal rate of change above threshold</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>28</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>signal bias level out of range / zero adjustment failure</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>29</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>signal invalid</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>2A</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>signal stuck in range</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>2B</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>signal cross coupled</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>2F</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>signal erratic</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>31</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>No Signal</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>32</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Signal Low Time &lt; Minimum</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>33</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Signal Low Time &gt; Maximum</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>34</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Signal High Time &lt; Minimum</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>35</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Signal High Time &gt; Maximum</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>36</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Signal Frequency Too Low</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>37</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Signal Frequency Too High</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>38</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Signal Frequency Incorrect</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>39</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Signal Has Too Few Pulses</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>3A</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Signal Has Too Many Pulses</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>41</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>general checksum failure</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>42</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>general memory failure</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>43</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>special memory failure</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>44</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>data memory failure</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>45</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>program memory failure</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>46</v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>calibration / parameter memory failure</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>47</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>watchdog / safety MicroController failure</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>48</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>supervision software failure</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>49</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>internal electronic failure</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>4A</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>Incorrect Component Installed</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>4B</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>over temperature</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>51</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>not programmed</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>52</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>not activated</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>53</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>deactivated</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>54</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>missing calibration</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>55</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>not configured</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>56</v>
+          </cell>
+          <cell r="B65" t="str">
+            <v>Invalid / incomplete configuration</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>57</v>
+          </cell>
+          <cell r="B66" t="str">
+            <v>invalid / incomplete software component</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>61</v>
+          </cell>
+          <cell r="B67" t="str">
+            <v>signal calculation failure</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>62</v>
+          </cell>
+          <cell r="B68" t="str">
+            <v>signal compare failure</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>63</v>
+          </cell>
+          <cell r="B69" t="str">
+            <v>circuit / component protection time-out</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>64</v>
+          </cell>
+          <cell r="B70" t="str">
+            <v>signal plausibility failure</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>65</v>
+          </cell>
+          <cell r="B71" t="str">
+            <v>signal has too few transitions / events</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>66</v>
+          </cell>
+          <cell r="B72" t="str">
+            <v>signal has too many transitions / events</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>67</v>
+          </cell>
+          <cell r="B73" t="str">
+            <v>supervision software failure</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>68</v>
+          </cell>
+          <cell r="B74" t="str">
+            <v>event information</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>71</v>
+          </cell>
+          <cell r="B75" t="str">
+            <v>actuator stuck</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>72</v>
+          </cell>
+          <cell r="B76" t="str">
+            <v>actuator stuck open</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>73</v>
+          </cell>
+          <cell r="B77" t="str">
+            <v>actuator stuck closed</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>74</v>
+          </cell>
+          <cell r="B78" t="str">
+            <v>actuator slipping</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>75</v>
+          </cell>
+          <cell r="B79" t="str">
+            <v>emergency position not reachable</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>76</v>
+          </cell>
+          <cell r="B80" t="str">
+            <v>wrong mounting position</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>77</v>
+          </cell>
+          <cell r="B81" t="str">
+            <v>commanded position not reachable</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>78</v>
+          </cell>
+          <cell r="B82" t="str">
+            <v>alignment or adjustment incorrect</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>79</v>
+          </cell>
+          <cell r="B83" t="str">
+            <v xml:space="preserve">mechanical linkage failure </v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>7A</v>
+          </cell>
+          <cell r="B84" t="str">
+            <v>fluid leak or seal failure</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>7B</v>
+          </cell>
+          <cell r="B85" t="str">
+            <v>low fluid level</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>81</v>
+          </cell>
+          <cell r="B86" t="str">
+            <v>invalid serial data received</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>82</v>
+          </cell>
+          <cell r="B87" t="str">
+            <v>alive / sequence counter incorrect / not updated</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>83</v>
+          </cell>
+          <cell r="B88" t="str">
+            <v>value of signal protection calculation incorrect</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>84</v>
+          </cell>
+          <cell r="B89" t="str">
+            <v>signal below allowable range</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>85</v>
+          </cell>
+          <cell r="B90" t="str">
+            <v>signal above allowable range</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>86</v>
+          </cell>
+          <cell r="B91" t="str">
+            <v>signal invalid</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>87</v>
+          </cell>
+          <cell r="B92" t="str">
+            <v>missing message</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>88</v>
+          </cell>
+          <cell r="B93" t="str">
+            <v>bus off</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>8F</v>
+          </cell>
+          <cell r="B94" t="str">
+            <v>erratic</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>91</v>
+          </cell>
+          <cell r="B95" t="str">
+            <v>parametric</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>92</v>
+          </cell>
+          <cell r="B96" t="str">
+            <v>performance or incorrect operation</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>93</v>
+          </cell>
+          <cell r="B97" t="str">
+            <v>no operation</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>94</v>
+          </cell>
+          <cell r="B98" t="str">
+            <v>unexpected operation</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>95</v>
+          </cell>
+          <cell r="B99" t="str">
+            <v>incorrect assembly</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>96</v>
+          </cell>
+          <cell r="B100" t="str">
+            <v>component internal failure</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>97</v>
+          </cell>
+          <cell r="B101" t="str">
+            <v>Component or system operation obstructed or blocked</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>98</v>
+          </cell>
+          <cell r="B102" t="str">
+            <v>component or system over temperature</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>9A</v>
+          </cell>
+          <cell r="B103" t="str">
+            <v>component or system operating conditions</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5589,6 +6703,10 @@
       <sheetName val="Events"/>
       <sheetName val="Ref_DSVars"/>
       <sheetName val="Ref_SecurityLevels"/>
+      <sheetName val="DiagRoutine (0E00)"/>
+      <sheetName val="DiagRoutine (0E12)"/>
+      <sheetName val="DiagRoutine (0E13)"/>
+      <sheetName val="DiagRoutine (0E01)"/>
       <sheetName val="Selections"/>
     </sheetNames>
     <sheetDataSet>
@@ -5701,7 +6819,11 @@
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
-      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="109"/>
+      <sheetData sheetId="110"/>
+      <sheetData sheetId="111"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5950,6 +7072,855 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="Macro1"/>
+      <sheetName val="封面"/>
+      <sheetName val="RevisionRecords"/>
+      <sheetName val="Content"/>
+      <sheetName val="1.General"/>
+      <sheetName val="2.DiagnosticServices"/>
+      <sheetName val="3.TimingParameters"/>
+      <sheetName val="snFyHQ"/>
+      <sheetName val="4.1 DIDList"/>
+      <sheetName val="4.2 IODIDList"/>
+      <sheetName val="4.3 RoutineDIDList"/>
+      <sheetName val="5.1 DTCs list"/>
+      <sheetName val="5.2 Status of DTC"/>
+      <sheetName val="5.3 DTCSnapshot&amp;Extended"/>
+      <sheetName val="6.Security Access"/>
+      <sheetName val="discuss list"/>
+      <sheetName val="Ref_Ranges"/>
+      <sheetName val="Header"/>
+      <sheetName val="Selections"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fault_List"/>
+      <sheetName val="Selections"/>
+      <sheetName val="1.General"/>
+      <sheetName val="Ref_Ranges"/>
+      <sheetName val="Header"/>
+      <sheetName val="DataBlock"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Rule"/>
+      <sheetName val="GeneralInfo"/>
+      <sheetName val="diagnosis services"/>
+      <sheetName val="Precondition_clarify"/>
+      <sheetName val="System DID"/>
+      <sheetName val="ECU DID"/>
+      <sheetName val="IOControl (0x2F)"/>
+      <sheetName val="Routines (0x31)"/>
+      <sheetName val="DTC_list_J2012DA"/>
+      <sheetName val="DTC-List"/>
+      <sheetName val="Error_Code"/>
+      <sheetName val="Fault Class Def"/>
+      <sheetName val="Env Set"/>
+      <sheetName val="PartNumber"/>
+      <sheetName val="DTC_List(old)"/>
+      <sheetName val="DTC_Ranges"/>
+      <sheetName val="DTC_Ranges_LIN"/>
+      <sheetName val="DTC_Checklist"/>
+      <sheetName val="Coding"/>
+      <sheetName val="Flash"/>
+      <sheetName val="DataBlock"/>
+      <sheetName val="Snapshot"/>
+      <sheetName val="Snapshot_local"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Ref_Ranges"/>
+      <sheetName val="Header"/>
+      <sheetName val="1.General"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="VF31 REQ External Discussion"/>
+      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
+      <sheetName val="Selections"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="VF31 REQ External Discussion"/>
+      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
+      <sheetName val="Selections"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="VF31 REQ External Discussion"/>
+      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
+      <sheetName val="Selections"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fault_List"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="Selections"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="TML_ECU_Specific_DTC_Template_L"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fault List"/>
+      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="PDU"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="DataBlock"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>00</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>01</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>02</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>03</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>04</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>05</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>06</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>07</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>08</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>09</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>1A</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>1B</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>1C</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>1D</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>1E</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>1F</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>2A</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>2B</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>2F</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>3A</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>4A</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>4B</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>54</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>57</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>61</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>63</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>64</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>65</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>67</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>71</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>73</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>74</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>75</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>76</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>78</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>79</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>7A</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>7B</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>81</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>82</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>83</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>84</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>86</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>87</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>8F</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>92</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>9A</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Terms and Acronyms"/>
+      <sheetName val="Fault List"/>
+      <sheetName val="Fauth_List_Future"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Notes"/>
+      <sheetName val="SelfTestDTC"/>
+      <sheetName val="DTC Guidelines"/>
+      <sheetName val="PDU"/>
+      <sheetName val="Sheet3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Change History"/>
+      <sheetName val="Acronyms and Terms"/>
+      <sheetName val="DID Quick Reference"/>
+      <sheetName val="DIDs from Other ECUs "/>
+      <sheetName val="Packeted"/>
+      <sheetName val="Numeric"/>
+      <sheetName val="StateEncoded"/>
+      <sheetName val="BitMapped"/>
+      <sheetName val="ASCII"/>
+      <sheetName val="BCD"/>
+      <sheetName val="Hex"/>
+      <sheetName val="Selections"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Missing DID"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
       <sheetName val="Header"/>
       <sheetName val="Network Config"/>
       <sheetName val="Change Details"/>
@@ -6059,10 +8030,6 @@
       <sheetName val="Events"/>
       <sheetName val="Ref_DSVars"/>
       <sheetName val="Ref_SecurityLevels"/>
-      <sheetName val="DiagRoutine (0E00)"/>
-      <sheetName val="DiagRoutine (0E12)"/>
-      <sheetName val="DiagRoutine (0E13)"/>
-      <sheetName val="DiagRoutine (0E01)"/>
       <sheetName val="Selections"/>
     </sheetNames>
     <sheetDataSet>
@@ -6175,1796 +8142,7 @@
       <sheetData sheetId="106"/>
       <sheetData sheetId="107"/>
       <sheetData sheetId="108"/>
-      <sheetData sheetId="109"/>
-      <sheetData sheetId="110"/>
-      <sheetData sheetId="111"/>
-      <sheetData sheetId="112" refreshError="1"/>
-      <sheetData sheetId="113" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Macro1"/>
-      <sheetName val="封面"/>
-      <sheetName val="RevisionRecords"/>
-      <sheetName val="Content"/>
-      <sheetName val="1.General"/>
-      <sheetName val="2.DiagnosticServices"/>
-      <sheetName val="3.TimingParameters"/>
-      <sheetName val="snFyHQ"/>
-      <sheetName val="4.1 DIDList"/>
-      <sheetName val="4.2 IODIDList"/>
-      <sheetName val="4.3 RoutineDIDList"/>
-      <sheetName val="5.1 DTCs list"/>
-      <sheetName val="5.2 Status of DTC"/>
-      <sheetName val="5.3 DTCSnapshot&amp;Extended"/>
-      <sheetName val="6.Security Access"/>
-      <sheetName val="discuss list"/>
-      <sheetName val="Ref_Ranges"/>
-      <sheetName val="Header"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fault_List"/>
-      <sheetName val="Selections"/>
-      <sheetName val="1.General"/>
-      <sheetName val="Ref_Ranges"/>
-      <sheetName val="Header"/>
-      <sheetName val="DataBlock"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Rule"/>
-      <sheetName val="GeneralInfo"/>
-      <sheetName val="diagnosis services"/>
-      <sheetName val="Precondition_clarify"/>
-      <sheetName val="System DID"/>
-      <sheetName val="ECU DID"/>
-      <sheetName val="IOControl (0x2F)"/>
-      <sheetName val="Routines (0x31)"/>
-      <sheetName val="DTC_list_J2012DA"/>
-      <sheetName val="DTC-List"/>
-      <sheetName val="Error_Code"/>
-      <sheetName val="Fault Class Def"/>
-      <sheetName val="Env Set"/>
-      <sheetName val="PartNumber"/>
-      <sheetName val="DTC_List(old)"/>
-      <sheetName val="DTC_Ranges"/>
-      <sheetName val="DTC_Ranges_LIN"/>
-      <sheetName val="DTC_Checklist"/>
-      <sheetName val="Coding"/>
-      <sheetName val="Flash"/>
-      <sheetName val="DataBlock"/>
-      <sheetName val="Snapshot"/>
-      <sheetName val="Snapshot_local"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Ref_Ranges"/>
-      <sheetName val="Header"/>
-      <sheetName val="1.General"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Fault List"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fauth_List_Future"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="PDU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>no sub type information</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>Body</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>No</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>A1</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>MO</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>Gen</v>
-          </cell>
-          <cell r="I2">
-            <v>1</v>
-          </cell>
-          <cell r="J2" t="str">
-            <v>OPC</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>01</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>General Electrical Failure</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>Chassis</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>Yes</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>A2</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>WLO</v>
-          </cell>
-          <cell r="H3" t="str">
-            <v>Dev</v>
-          </cell>
-          <cell r="I3">
-            <v>2</v>
-          </cell>
-          <cell r="J3" t="str">
-            <v>MPC</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>02</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>General signal failure</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>Network</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>B</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>WLB</v>
-          </cell>
-          <cell r="I4">
-            <v>3</v>
-          </cell>
-          <cell r="J4" t="str">
-            <v>See FDC Strategy Columns</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>03</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>FM (Frequency Modulated) / PWM (Pulse Width Modulated) Failure</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>Powertrain</v>
-          </cell>
-          <cell r="F5" t="str">
-            <v>C</v>
-          </cell>
-          <cell r="G5" t="str">
-            <v>Generic Warning Text</v>
-          </cell>
-          <cell r="I5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>04</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>System Internal Failures</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>D</v>
-          </cell>
-          <cell r="G6" t="str">
-            <v>Specific Warning Text</v>
-          </cell>
-          <cell r="I6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>05</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>System Programming Failures</v>
-          </cell>
-          <cell r="F7" t="str">
-            <v>E</v>
-          </cell>
-          <cell r="G7" t="str">
-            <v>None</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>06</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Algorithm Based Failures</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>07</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Mechanical Failures</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>08</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Bus Signal / Message Failures</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>09</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Component Failures</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>circuit short to ground</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>12</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>circuit short to battery</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>circuit open</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>circuit short to ground or open</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>circuit short to battery or open</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>circuit voltage below threshold</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>17</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>circuit voltage above threshold</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>18</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>circuit current below threshold</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>19</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>circuit current above threshold</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>1A</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>circuit resistance below threshold</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>1B</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>circuit resistance above threshold</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>1C</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>circuit voltage out of range</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>1D</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>circuit current out of range</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>1E</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>circuit resistance out of range</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>1F</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>circuit intermittent</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>21</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>signal amplitude &lt; minimum</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>22</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>signal amplitude &gt; maximum</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>23</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>signal stuck low</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>24</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>signal stuck high</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>25</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>signal shape / waveform failure</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>26</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>signal rate of change below threshold</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>27</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>signal rate of change above threshold</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>28</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>signal bias level out of range / zero adjustment failure</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>29</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>signal invalid</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>2A</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>signal stuck in range</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>2B</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>signal cross coupled</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>2F</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>signal erratic</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>31</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>No Signal</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>32</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Signal Low Time &lt; Minimum</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>33</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Signal Low Time &gt; Maximum</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>34</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Signal High Time &lt; Minimum</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>35</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Signal High Time &gt; Maximum</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>36</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Signal Frequency Too Low</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>37</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Signal Frequency Too High</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>38</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Signal Frequency Incorrect</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>39</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Signal Has Too Few Pulses</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>3A</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Signal Has Too Many Pulses</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>41</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>general checksum failure</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>42</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>general memory failure</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>43</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>special memory failure</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>44</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>data memory failure</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>45</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>program memory failure</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>46</v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>calibration / parameter memory failure</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>47</v>
-          </cell>
-          <cell r="B55" t="str">
-            <v>watchdog / safety MicroController failure</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>48</v>
-          </cell>
-          <cell r="B56" t="str">
-            <v>supervision software failure</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>49</v>
-          </cell>
-          <cell r="B57" t="str">
-            <v>internal electronic failure</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>4A</v>
-          </cell>
-          <cell r="B58" t="str">
-            <v>Incorrect Component Installed</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>4B</v>
-          </cell>
-          <cell r="B59" t="str">
-            <v>over temperature</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>51</v>
-          </cell>
-          <cell r="B60" t="str">
-            <v>not programmed</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>52</v>
-          </cell>
-          <cell r="B61" t="str">
-            <v>not activated</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>53</v>
-          </cell>
-          <cell r="B62" t="str">
-            <v>deactivated</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>54</v>
-          </cell>
-          <cell r="B63" t="str">
-            <v>missing calibration</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>55</v>
-          </cell>
-          <cell r="B64" t="str">
-            <v>not configured</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>56</v>
-          </cell>
-          <cell r="B65" t="str">
-            <v>Invalid / incomplete configuration</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>57</v>
-          </cell>
-          <cell r="B66" t="str">
-            <v>invalid / incomplete software component</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>61</v>
-          </cell>
-          <cell r="B67" t="str">
-            <v>signal calculation failure</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>62</v>
-          </cell>
-          <cell r="B68" t="str">
-            <v>signal compare failure</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>63</v>
-          </cell>
-          <cell r="B69" t="str">
-            <v>circuit / component protection time-out</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>64</v>
-          </cell>
-          <cell r="B70" t="str">
-            <v>signal plausibility failure</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>65</v>
-          </cell>
-          <cell r="B71" t="str">
-            <v>signal has too few transitions / events</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>66</v>
-          </cell>
-          <cell r="B72" t="str">
-            <v>signal has too many transitions / events</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>67</v>
-          </cell>
-          <cell r="B73" t="str">
-            <v>supervision software failure</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>68</v>
-          </cell>
-          <cell r="B74" t="str">
-            <v>event information</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>71</v>
-          </cell>
-          <cell r="B75" t="str">
-            <v>actuator stuck</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>72</v>
-          </cell>
-          <cell r="B76" t="str">
-            <v>actuator stuck open</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>73</v>
-          </cell>
-          <cell r="B77" t="str">
-            <v>actuator stuck closed</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>74</v>
-          </cell>
-          <cell r="B78" t="str">
-            <v>actuator slipping</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>75</v>
-          </cell>
-          <cell r="B79" t="str">
-            <v>emergency position not reachable</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>76</v>
-          </cell>
-          <cell r="B80" t="str">
-            <v>wrong mounting position</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>77</v>
-          </cell>
-          <cell r="B81" t="str">
-            <v>commanded position not reachable</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>78</v>
-          </cell>
-          <cell r="B82" t="str">
-            <v>alignment or adjustment incorrect</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>79</v>
-          </cell>
-          <cell r="B83" t="str">
-            <v xml:space="preserve">mechanical linkage failure </v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>7A</v>
-          </cell>
-          <cell r="B84" t="str">
-            <v>fluid leak or seal failure</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>7B</v>
-          </cell>
-          <cell r="B85" t="str">
-            <v>low fluid level</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>81</v>
-          </cell>
-          <cell r="B86" t="str">
-            <v>invalid serial data received</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>82</v>
-          </cell>
-          <cell r="B87" t="str">
-            <v>alive / sequence counter incorrect / not updated</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>83</v>
-          </cell>
-          <cell r="B88" t="str">
-            <v>value of signal protection calculation incorrect</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>84</v>
-          </cell>
-          <cell r="B89" t="str">
-            <v>signal below allowable range</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>85</v>
-          </cell>
-          <cell r="B90" t="str">
-            <v>signal above allowable range</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>86</v>
-          </cell>
-          <cell r="B91" t="str">
-            <v>signal invalid</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>87</v>
-          </cell>
-          <cell r="B92" t="str">
-            <v>missing message</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>88</v>
-          </cell>
-          <cell r="B93" t="str">
-            <v>bus off</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>8F</v>
-          </cell>
-          <cell r="B94" t="str">
-            <v>erratic</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>91</v>
-          </cell>
-          <cell r="B95" t="str">
-            <v>parametric</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>92</v>
-          </cell>
-          <cell r="B96" t="str">
-            <v>performance or incorrect operation</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>93</v>
-          </cell>
-          <cell r="B97" t="str">
-            <v>no operation</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>94</v>
-          </cell>
-          <cell r="B98" t="str">
-            <v>unexpected operation</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>95</v>
-          </cell>
-          <cell r="B99" t="str">
-            <v>incorrect assembly</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>96</v>
-          </cell>
-          <cell r="B100" t="str">
-            <v>component internal failure</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>97</v>
-          </cell>
-          <cell r="B101" t="str">
-            <v>Component or system operation obstructed or blocked</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>98</v>
-          </cell>
-          <cell r="B102" t="str">
-            <v>component or system over temperature</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>9A</v>
-          </cell>
-          <cell r="B103" t="str">
-            <v>component or system operating conditions</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="VF31 REQ External Discussion"/>
-      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="VF31 REQ External Discussion"/>
-      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="VF31 REQ External Discussion"/>
-      <sheetName val="VFe34_GauTui_Requirement_Discus"/>
-      <sheetName val="Selections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fault_List"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="Selections"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="TML_ECU_Specific_DTC_Template_L"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fault List"/>
-      <sheetName val="Fauth_List_Future"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="PDU"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="DataBlock"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>00</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>01</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>02</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>03</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>04</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>05</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>06</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>07</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>08</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>09</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>1A</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>1B</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>1C</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>1D</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>1E</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>1F</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>23</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>25</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>2A</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>2B</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>2F</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>32</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>3A</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>46</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>47</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>4A</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>4B</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>57</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>63</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>64</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>65</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>67</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>68</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>71</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>73</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>74</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>75</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>76</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>78</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>79</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>7A</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>7B</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>81</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>82</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>83</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>84</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>86</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>87</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>88</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>8F</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>92</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>93</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>96</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>98</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>9A</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Terms and Acronyms"/>
-      <sheetName val="Fault List"/>
-      <sheetName val="Fauth_List_Future"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Notes"/>
-      <sheetName val="SelfTestDTC"/>
-      <sheetName val="DTC Guidelines"/>
-      <sheetName val="PDU"/>
-      <sheetName val="Sheet3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Change History"/>
-      <sheetName val="Acronyms and Terms"/>
-      <sheetName val="DID Quick Reference"/>
-      <sheetName val="DIDs from Other ECUs "/>
-      <sheetName val="Packeted"/>
-      <sheetName val="Numeric"/>
-      <sheetName val="StateEncoded"/>
-      <sheetName val="BitMapped"/>
-      <sheetName val="ASCII"/>
-      <sheetName val="BCD"/>
-      <sheetName val="Hex"/>
-      <sheetName val="Selections"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Missing DID"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8335,19 +8513,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1">
       <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="9" customFormat="1">
@@ -8393,13 +8571,11 @@
       <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>5</v>
-      </c>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" ht="79.2">
       <c r="A5" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="11">
         <v>13</v>
@@ -8411,12 +8587,12 @@
         <v>4</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="13" customFormat="1" ht="92.4">
+    <row r="6" spans="1:5" s="13" customFormat="1" ht="409.6">
       <c r="A6" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="11">
         <v>14</v>
@@ -8428,12 +8604,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="13" customFormat="1" ht="330">
       <c r="A7" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="11">
         <v>15</v>
@@ -8445,12 +8621,12 @@
         <v>8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="13" customFormat="1" ht="409.6">
       <c r="A8" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="11">
         <v>16</v>
@@ -8462,12 +8638,12 @@
         <v>4</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="13" customFormat="1" ht="79.2">
       <c r="A9" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="15">
         <v>17</v>
@@ -8479,12 +8655,12 @@
         <v>4</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="13" customFormat="1">
       <c r="A10" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="18">
         <v>17</v>
@@ -8499,7 +8675,7 @@
     </row>
     <row r="11" spans="1:5" s="13" customFormat="1" ht="66">
       <c r="A11" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="15">
         <v>18</v>
@@ -8511,12 +8687,12 @@
         <v>4</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="13" customFormat="1" ht="66">
       <c r="A12" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="15">
         <v>18</v>
@@ -8528,12 +8704,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" ht="66">
       <c r="A13" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="15">
         <v>19</v>
@@ -8545,12 +8721,12 @@
         <v>4</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="13" customFormat="1" ht="66">
       <c r="A14" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="15">
         <v>19</v>
@@ -8562,12 +8738,12 @@
         <v>4</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="1" customFormat="1">
       <c r="A15" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="7">
         <v>61</v>
@@ -8590,11 +8766,11 @@
     <cfRule type="duplicateValues" dxfId="49" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="53"/>
     <cfRule type="duplicateValues" dxfId="43" priority="55"/>
     <cfRule type="duplicateValues" dxfId="42" priority="56"/>
   </conditionalFormatting>
@@ -8602,21 +8778,21 @@
     <cfRule type="duplicateValues" dxfId="41" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
     <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
     <cfRule type="duplicateValues" dxfId="27" priority="2"/>
@@ -8628,31 +8804,31 @@
     <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="24"/>
     <cfRule type="duplicateValues" dxfId="10" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
     <cfRule type="duplicateValues" dxfId="6" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51111111111111096" footer="0.51111111111111096"/>
   <pageSetup paperSize="9" orientation="portrait"/>
